--- a/rpa/report.xlsx
+++ b/rpa/report.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/rpa/report.xlsx
+++ b/rpa/report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,22 +441,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1,000 Places to See Before You Die</t>
+          <t>A Flight of Arrows (The Pathfinders #2)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Â£26.08</t>
+          <t>Â£55.53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/1,000_Places_to_See_Before_You_Die</t>
+          <t>https://en.wikipedia.org/wiki/Special:Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mrs. Houdini</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Â£30.25</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/w/index.php?search=A+Flight+of+Arrows+%28The+Pathfinders+%232%29&amp;title=Special%3ASearch&amp;profile=advanced&amp;fulltext=1&amp;ns0=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>The Passion of Dolssa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Â£28.32</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/w/index.php?search=A+Flight+of+Arrows+%28The+Pathfinders+%232%29Mrs.+HoudiniThe+Passion+of+Dolssa&amp;title=Special%3ASearch&amp;profile=advanced&amp;fulltext=1&amp;ns0=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Voyager (Outlander #3)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Â£21.07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/w/index.php?search=Voyager+%28Outlander+%233%29&amp;title=Special%3ASearch&amp;profile=advanced&amp;fulltext=1&amp;ns0=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>The Red Tent</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Â£35.66</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/w/index.php?search=The+Red+Tent&amp;title=Special%3ASearch&amp;profile=advanced&amp;fulltext=1&amp;ns0=1</t>
         </is>
       </c>
     </row>

--- a/rpa/report.xlsx
+++ b/rpa/report.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Special:Search</t>
+          <t>No result</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/w/index.php?search=A+Flight+of+Arrows+%28The+Pathfinders+%232%29&amp;title=Special%3ASearch&amp;profile=advanced&amp;fulltext=1&amp;ns0=1</t>
+          <t>No result</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/w/index.php?search=A+Flight+of+Arrows+%28The+Pathfinders+%232%29Mrs.+HoudiniThe+Passion+of+Dolssa&amp;title=Special%3ASearch&amp;profile=advanced&amp;fulltext=1&amp;ns0=1</t>
+          <t>No result</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/w/index.php?search=Voyager+%28Outlander+%233%29&amp;title=Special%3ASearch&amp;profile=advanced&amp;fulltext=1&amp;ns0=1</t>
+          <t>No result</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/w/index.php?search=The+Red+Tent&amp;title=Special%3ASearch&amp;profile=advanced&amp;fulltext=1&amp;ns0=1</t>
+          <t>No result</t>
         </is>
       </c>
     </row>
